--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Tassa sui rifiuti (TARI).xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Tassa sui rifiuti (TARI).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="103">
   <si>
     <r>
       <t xml:space="preserve">
@@ -76,19 +76,19 @@
     <t>Messaggi presenti in questo template</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione di occupazione </t>
+    <t>Dichiarazione di occupazione</t>
   </si>
   <si>
     <t>Dichiarazione di occupazione: accolta</t>
   </si>
   <si>
-    <t xml:space="preserve">Avviso di pagamento TARI </t>
+    <t>Avviso di pagamento TARI</t>
   </si>
   <si>
     <t>Avviso di pagamento TARI: in scadenza</t>
   </si>
   <si>
-    <t xml:space="preserve">Istruzioni sul pagamento della rata </t>
+    <t>Istruzioni sul pagamento della rata</t>
   </si>
   <si>
     <t>Proroga scadenza del pagamento</t>
@@ -145,7 +145,7 @@
     <t>Inserire una descrizione del servizio e delle tipologie di pagamenti che si potranno effettuare per il servizio.</t>
   </si>
   <si>
-    <t xml:space="preserve">Il servizio riguarda la Tassa sui rifiuti (TARI). 
+    <t xml:space="preserve">Il servizio riguarda la Tassa sui rifiuti (TARI).
 Tramite IO potrai:
 - ricevere conferma della dichiarazione di occupazione di un immobile domestico e non domestico al fine della TARI;
 - ricevere avvisi di pagamento relativi alla TARI e pagarli in app;
@@ -160,7 +160,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>n/a</t>
+    <t>Vai al servizio</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -425,8 +425,8 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
-Ricevi questo messaggio perché potresti avere recentemente cambiato residenza, acquistato un immobile o sottoscritto un contratto di affitto. 
+      <t xml:space="preserve">.
+Ricevi questo messaggio perché potresti avere recentemente cambiato residenza, acquistato un immobile o sottoscritto un contratto di affitto.
 Se non lo hai già fatto, effettua o aggiorna la tua dichiarazione di occupazione ai fini TARI (Tassa sui Rifiuti). Per farlo, [visita questo sito](URL).
 Inoltre, se vuoi conoscere meglio il servizio offerto [visita questo sito](URL).</t>
     </r>
@@ -507,7 +507,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> 
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -784,7 +784,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> sarà possibile pagare la Tassa sui rifiuti (TARI)  intestato a </t>
+      <t xml:space="preserve"> sarà possibile pagare la Tassa sui rifiuti (TARI) intestato a </t>
     </r>
     <r>
       <rPr>
@@ -845,7 +845,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -933,7 +933,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> € 
+      <t xml:space="preserve"> €
 </t>
     </r>
     <r>
@@ -969,7 +969,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -981,7 +981,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">Abbiamo ricevuto la tua dichiarazione di cessazione occupazione immobile. 
+      <t xml:space="preserve">Abbiamo ricevuto la tua dichiarazione di cessazione occupazione immobile.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.</t>
     </r>
   </si>
@@ -1005,9 +1005,6 @@
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1025,7 +1022,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1099,15 +1096,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
   </si>
 </sst>
 </file>
@@ -1826,7 +1814,7 @@
         <v>85</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" s="34" t="s">
         <v>85</v>
@@ -1834,7 +1822,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>57</v>
@@ -1860,7 +1848,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>85</v>
@@ -1875,7 +1863,7 @@
         <v>85</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8" s="34" t="s">
         <v>85</v>
@@ -1886,59 +1874,59 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="C9" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="D9" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="E9" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="H9" s="34" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="B10" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="C10" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="D10" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="E10" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="F10" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="F10" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="G10" s="34" t="s">
+      <c r="H10" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="H10" s="34" t="s">
-        <v>102</v>
-      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>57</v>
@@ -1950,10 +1938,10 @@
         <v>57</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="G11" s="34" t="s">
         <v>57</v>
